--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260812.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.60%</t>
+          <t>9.54%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.90%</t>
+          <t>9.07%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.12%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.63%</t>
+          <t>6.58%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>台指期貨</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,940</t>
+          <t>5,900,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.78%</t>
+          <t>5.59%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>5,801,000</t>
+          <t>2,443,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.25%</t>
         </is>
       </c>
     </row>
@@ -748,95 +748,95 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.19%</t>
+          <t>4.99%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,443,000</t>
+          <t>2,496,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>4.90%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,496,000</t>
+          <t>6,419,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.63%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>6,419,000</t>
+          <t>7,070,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.53%</t>
+          <t>4.12%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>7,070,000</t>
+          <t>9,634,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>9,519,000</t>
+          <t>87,718,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.51%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>87,718,000</t>
+          <t>2,375,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
@@ -924,73 +924,73 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,375,000</t>
+          <t>5,499,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>5,499,000</t>
+          <t>484,900</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台指期貨</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>454,900</t>
+          <t>679</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,215,000</t>
+          <t>2,265,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1117,100 +1117,100 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>572,000</t>
+          <t>622,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,174,000</t>
+          <t>478,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>361,000</t>
+          <t>2,424,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,682,000</t>
+          <t>802,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>712,000</t>
+          <t>1,682,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>140,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>140,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>18,595,909,210</t>
+          <t>18,687,493,543</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,709,392,006</t>
+          <t>1,824,416,742</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>359,154,498</t>
+          <t>-593,864,419</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
